--- a/data/synth/review_sheet_batch2.xlsx
+++ b/data/synth/review_sheet_batch2.xlsx
@@ -441,7 +441,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>合成句審核表 — 請手語老師／聾人顧問逐句確認 Gloss 與 NMS （審核結果填：通過／修正／不通過；rule-derived 句型請優先審核）</t>
+          <t>合成句審核表 — 請手語老師／聾人顧問逐句確認 Gloss 與 NMS （審核結果填：通過／修正／不通過；rule-derived 句型請優先審核）｜審核結果欄為 AI 語言學預審（依文獻＋語料實證）；標『需母語者裁定/確認』者仍須手語老師逐句覆核，非母語聾人最終判定</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -579,10 +585,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -620,10 +632,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -661,10 +679,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -702,10 +726,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -743,10 +773,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -784,10 +820,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -825,10 +867,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -866,10 +914,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -907,10 +961,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -948,10 +1008,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -989,10 +1055,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1030,10 +1102,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1071,10 +1149,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1112,10 +1196,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1153,10 +1243,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1194,10 +1290,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1235,10 +1337,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1276,10 +1384,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1317,10 +1431,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1358,10 +1478,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1399,10 +1525,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1440,10 +1572,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1481,10 +1619,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1522,10 +1666,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1563,10 +1713,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1604,10 +1760,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1645,10 +1807,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1686,10 +1854,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1727,10 +1901,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1768,10 +1948,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1809,10 +1995,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1850,10 +2042,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1891,10 +2089,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1932,10 +2136,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1973,10 +2183,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2014,10 +2230,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2055,10 +2277,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2096,10 +2324,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2137,10 +2371,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2178,10 +2418,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2219,10 +2465,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2260,10 +2512,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2301,10 +2559,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2342,10 +2606,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2383,10 +2653,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2424,10 +2700,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2465,10 +2747,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2506,10 +2794,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2547,10 +2841,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2588,10 +2888,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2629,10 +2935,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2670,10 +2982,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2711,10 +3029,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2752,10 +3076,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2793,10 +3123,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2834,10 +3170,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2875,10 +3217,16 @@
           <t>規則6 否定詞置動詞後（自有實例 S18 我不舒服→我/舒服/不）＋規則2 定居句語序（P01）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2916,10 +3264,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2957,10 +3311,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2998,10 +3358,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3039,10 +3405,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3080,10 +3452,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3121,10 +3499,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3162,10 +3546,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3203,10 +3593,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3244,10 +3640,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3285,10 +3687,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3326,10 +3734,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3367,10 +3781,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3408,10 +3828,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3449,10 +3875,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3490,10 +3922,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3531,10 +3969,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3572,10 +4016,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3613,10 +4063,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3654,10 +4110,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3695,10 +4157,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3736,10 +4204,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3777,10 +4251,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3818,10 +4298,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3859,10 +4345,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3900,10 +4392,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3941,10 +4439,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3982,10 +4486,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4023,10 +4533,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4064,10 +4580,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4105,10 +4627,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4146,10 +4674,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4187,10 +4721,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4228,10 +4768,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4269,10 +4815,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4310,10 +4862,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4351,10 +4909,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4392,10 +4956,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4433,10 +5003,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4474,10 +5050,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4515,10 +5097,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4556,10 +5144,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4597,10 +5191,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4638,10 +5238,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4679,10 +5285,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4720,10 +5332,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4761,10 +5379,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4802,10 +5426,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4843,10 +5473,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4884,10 +5520,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4925,10 +5567,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4966,10 +5614,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5007,10 +5661,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5048,10 +5708,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5089,10 +5755,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5130,10 +5802,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5171,10 +5849,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5212,10 +5896,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5253,10 +5943,16 @@
           <t>規則1 情態詞「要」句尾（T6／S14）＋規則3 是非問句 NMS 不比「嗎」（P03）。自有資料無此組合實例，審核優先</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5294,10 +5990,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5335,10 +6037,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5376,10 +6084,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5417,10 +6131,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5458,10 +6178,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5499,10 +6225,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5540,10 +6272,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5581,10 +6319,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5622,10 +6366,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5663,10 +6413,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5704,10 +6460,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5745,10 +6507,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5786,10 +6554,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5827,10 +6601,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5868,10 +6648,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5909,10 +6695,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5950,10 +6742,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5991,10 +6789,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6032,10 +6836,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6073,10 +6883,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6114,10 +6930,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6155,10 +6977,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6196,10 +7024,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6237,10 +7071,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6278,10 +7118,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6319,10 +7165,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6360,10 +7212,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6401,10 +7259,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6442,10 +7306,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6483,10 +7353,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6524,10 +7400,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6565,10 +7447,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6606,10 +7494,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6647,10 +7541,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6688,10 +7588,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6729,10 +7635,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6770,10 +7682,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6811,10 +7729,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6852,10 +7776,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6893,10 +7823,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6934,10 +7870,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6975,10 +7917,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7016,10 +7964,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7057,10 +8011,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7098,10 +8058,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7139,10 +8105,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7180,10 +8152,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7221,10 +8199,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7262,10 +8246,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7303,10 +8293,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7344,10 +8340,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7385,10 +8387,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7426,10 +8434,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7467,10 +8481,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7508,10 +8528,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7549,10 +8575,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7590,10 +8622,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7631,10 +8669,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7672,10 +8716,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7713,10 +8763,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7754,10 +8810,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7795,10 +8857,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7836,10 +8904,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7877,10 +8951,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7918,10 +8998,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7959,10 +9045,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8000,10 +9092,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8041,10 +9139,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8082,10 +9186,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8123,10 +9233,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8164,10 +9280,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8205,10 +9327,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8246,10 +9374,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8287,10 +9421,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -8328,10 +9468,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -8369,10 +9515,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -8410,10 +9562,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -8451,10 +9609,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -8492,10 +9656,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -8533,10 +9703,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8574,10 +9750,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -8615,10 +9797,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -8656,10 +9844,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr"/>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -8697,10 +9891,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -8738,10 +9938,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr"/>
-      <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -8779,10 +9985,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr"/>
-      <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -8820,10 +10032,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr"/>
-      <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -8861,10 +10079,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr"/>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -8902,10 +10126,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr"/>
-      <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -8943,10 +10173,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -8984,10 +10220,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr"/>
-      <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr"/>
-      <c r="K209" t="inlineStr"/>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -9025,10 +10267,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr"/>
-      <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -9066,10 +10314,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr"/>
-      <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -9107,10 +10361,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr"/>
-      <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -9148,10 +10408,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr"/>
-      <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -9189,10 +10455,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr"/>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -9230,10 +10502,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr"/>
-      <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -9271,10 +10549,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr"/>
-      <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -9312,10 +10596,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr"/>
-      <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -9353,10 +10643,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr"/>
-      <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -9394,10 +10690,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr"/>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -9435,10 +10737,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr"/>
-      <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -9476,10 +10784,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr"/>
-      <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -9517,10 +10831,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr"/>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -9558,10 +10878,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr"/>
-      <c r="I223" t="inlineStr"/>
-      <c r="J223" t="inlineStr"/>
-      <c r="K223" t="inlineStr"/>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -9599,10 +10925,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr"/>
-      <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -9640,10 +10972,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr"/>
-      <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -9681,10 +11019,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr"/>
-      <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -9722,10 +11066,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr"/>
-      <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -9763,10 +11113,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr"/>
-      <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -9804,10 +11160,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr"/>
-      <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -9845,10 +11207,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr"/>
-      <c r="I230" t="inlineStr"/>
-      <c r="J230" t="inlineStr"/>
-      <c r="K230" t="inlineStr"/>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -9886,10 +11254,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr"/>
-      <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
-      <c r="K231" t="inlineStr"/>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -9927,10 +11301,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr"/>
-      <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -9968,10 +11348,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr"/>
-      <c r="I233" t="inlineStr"/>
-      <c r="J233" t="inlineStr"/>
-      <c r="K233" t="inlineStr"/>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -10009,10 +11395,16 @@
           <t>規則1＋規則3＋規則5 時間詞句首之三規則組合（P04 語序＋P03 NMS），審核優先</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr"/>
-      <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 時間句首符82%；情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -10050,10 +11442,16 @@
           <t>規則1 情態詞句尾＋規則7 WH 句末；「哪裡」與「要」的相對順序由規則7（WH 句末）與規則1（情態句尾）競合，暫依 S14 語序推導「要」最尾，務必請老師確認，審核最優先</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr"/>
-      <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>需母語者裁定：WH「哪裡」與情態「要」句尾競合；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] Tai&amp;Tsay2015 未給此競合逐句答案；情態句尾68%、WH句末63% 皆傾向非絕對；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -10091,10 +11489,16 @@
           <t>T13＋規則5 時間詞句首。與 T13 同屬順序競合句型，審核最優先</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr"/>
-      <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>需母語者裁定：WH「哪裡」與情態「要」句尾競合；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] Tai&amp;Tsay2015 未給此競合逐句答案；情態句尾68%、WH句末63% 皆傾向非絕對；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -10132,10 +11536,16 @@
           <t>T13＋規則5 時間詞句首。與 T13 同屬順序競合句型，審核最優先</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr"/>
-      <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>需母語者裁定：WH「哪裡」與情態「要」句尾競合；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] Tai&amp;Tsay2015 未給此競合逐句答案；情態句尾68%、WH句末63% 皆傾向非絕對；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -10173,10 +11583,16 @@
           <t>T13＋規則5 時間詞句首。與 T13 同屬順序競合句型，審核最優先</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr"/>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>需母語者裁定：WH「哪裡」與情態「要」句尾競合；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] Tai&amp;Tsay2015 未給此競合逐句答案；情態句尾68%、WH句末63% 皆傾向非絕對；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -10214,10 +11630,16 @@
           <t>T13＋規則5 時間詞句首。與 T13 同屬順序競合句型，審核最優先</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr"/>
-      <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>需母語者裁定：WH「哪裡」與情態「要」句尾競合；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] Tai&amp;Tsay2015 未給此競合逐句答案；情態句尾68%、WH句末63% 皆傾向非絕對；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -10255,10 +11677,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr"/>
-      <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -10296,10 +11724,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr"/>
-      <c r="I241" t="inlineStr"/>
-      <c r="J241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -10337,10 +11771,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr"/>
-      <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -10378,10 +11818,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr"/>
-      <c r="I243" t="inlineStr"/>
-      <c r="J243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -10419,10 +11865,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr"/>
-      <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -10460,10 +11912,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr"/>
-      <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -10501,10 +11959,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr"/>
-      <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -10542,10 +12006,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr"/>
-      <c r="I247" t="inlineStr"/>
-      <c r="J247" t="inlineStr"/>
-      <c r="K247" t="inlineStr"/>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -10583,10 +12053,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr"/>
-      <c r="I248" t="inlineStr"/>
-      <c r="J248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -10624,10 +12100,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr"/>
-      <c r="I249" t="inlineStr"/>
-      <c r="J249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -10665,10 +12147,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr"/>
-      <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr"/>
-      <c r="K250" t="inlineStr"/>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -10706,10 +12194,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr"/>
-      <c r="I251" t="inlineStr"/>
-      <c r="J251" t="inlineStr"/>
-      <c r="K251" t="inlineStr"/>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -10747,10 +12241,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr"/>
-      <c r="I252" t="inlineStr"/>
-      <c r="J252" t="inlineStr"/>
-      <c r="K252" t="inlineStr"/>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -10788,10 +12288,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr"/>
-      <c r="I253" t="inlineStr"/>
-      <c r="J253" t="inlineStr"/>
-      <c r="K253" t="inlineStr"/>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -10829,10 +12335,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr"/>
-      <c r="I254" t="inlineStr"/>
-      <c r="J254" t="inlineStr"/>
-      <c r="K254" t="inlineStr"/>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -10870,10 +12382,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr"/>
-      <c r="I255" t="inlineStr"/>
-      <c r="J255" t="inlineStr"/>
-      <c r="K255" t="inlineStr"/>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -10911,10 +12429,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr"/>
-      <c r="I256" t="inlineStr"/>
-      <c r="J256" t="inlineStr"/>
-      <c r="K256" t="inlineStr"/>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -10952,10 +12476,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr"/>
-      <c r="I257" t="inlineStr"/>
-      <c r="J257" t="inlineStr"/>
-      <c r="K257" t="inlineStr"/>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -10993,10 +12523,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr"/>
-      <c r="I258" t="inlineStr"/>
-      <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr"/>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -11034,10 +12570,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr"/>
-      <c r="I259" t="inlineStr"/>
-      <c r="J259" t="inlineStr"/>
-      <c r="K259" t="inlineStr"/>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -11075,10 +12617,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr"/>
-      <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -11116,10 +12664,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr"/>
-      <c r="I261" t="inlineStr"/>
-      <c r="J261" t="inlineStr"/>
-      <c r="K261" t="inlineStr"/>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -11157,10 +12711,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr"/>
-      <c r="I262" t="inlineStr"/>
-      <c r="J262" t="inlineStr"/>
-      <c r="K262" t="inlineStr"/>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -11198,10 +12758,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr"/>
-      <c r="I263" t="inlineStr"/>
-      <c r="J263" t="inlineStr"/>
-      <c r="K263" t="inlineStr"/>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -11239,10 +12805,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr"/>
-      <c r="I264" t="inlineStr"/>
-      <c r="J264" t="inlineStr"/>
-      <c r="K264" t="inlineStr"/>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -11280,10 +12852,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr"/>
-      <c r="I265" t="inlineStr"/>
-      <c r="J265" t="inlineStr"/>
-      <c r="K265" t="inlineStr"/>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -11321,10 +12899,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr"/>
-      <c r="I266" t="inlineStr"/>
-      <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr"/>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -11362,10 +12946,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr"/>
-      <c r="I267" t="inlineStr"/>
-      <c r="J267" t="inlineStr"/>
-      <c r="K267" t="inlineStr"/>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -11403,10 +12993,16 @@
           <t>T8 之無時間詞形：規則6 否定詞置動詞後（Jane Tsay 2021 TODAY-I-SCHOOL-GO-NOT 去掉時間詞），審核優先</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr"/>
-      <c r="I268" t="inlineStr"/>
-      <c r="J268" t="inlineStr"/>
-      <c r="K268" t="inlineStr"/>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -11444,10 +13040,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr"/>
-      <c r="I269" t="inlineStr"/>
-      <c r="J269" t="inlineStr"/>
-      <c r="K269" t="inlineStr"/>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -11485,10 +13087,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr"/>
-      <c r="I270" t="inlineStr"/>
-      <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr"/>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -11526,10 +13134,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr"/>
-      <c r="I271" t="inlineStr"/>
-      <c r="J271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -11567,10 +13181,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr"/>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -11608,10 +13228,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr"/>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -11649,10 +13275,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr"/>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -11690,10 +13322,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr"/>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -11731,10 +13369,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr"/>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -11772,10 +13416,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr"/>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -11813,10 +13463,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr"/>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -11854,10 +13510,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr"/>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -11895,10 +13557,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr"/>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -11936,10 +13604,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr"/>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -11977,10 +13651,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr"/>
-      <c r="I282" t="inlineStr"/>
-      <c r="J282" t="inlineStr"/>
-      <c r="K282" t="inlineStr"/>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -12018,10 +13698,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr"/>
-      <c r="I283" t="inlineStr"/>
-      <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr"/>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -12059,10 +13745,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr"/>
-      <c r="I284" t="inlineStr"/>
-      <c r="J284" t="inlineStr"/>
-      <c r="K284" t="inlineStr"/>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -12100,10 +13792,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr"/>
-      <c r="I285" t="inlineStr"/>
-      <c r="J285" t="inlineStr"/>
-      <c r="K285" t="inlineStr"/>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -12141,10 +13839,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr"/>
-      <c r="I286" t="inlineStr"/>
-      <c r="J286" t="inlineStr"/>
-      <c r="K286" t="inlineStr"/>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -12182,10 +13886,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr"/>
-      <c r="I287" t="inlineStr"/>
-      <c r="J287" t="inlineStr"/>
-      <c r="K287" t="inlineStr"/>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -12223,10 +13933,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr"/>
-      <c r="I288" t="inlineStr"/>
-      <c r="J288" t="inlineStr"/>
-      <c r="K288" t="inlineStr"/>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -12264,10 +13980,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr"/>
-      <c r="I289" t="inlineStr"/>
-      <c r="J289" t="inlineStr"/>
-      <c r="K289" t="inlineStr"/>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -12305,10 +14027,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr"/>
-      <c r="I290" t="inlineStr"/>
-      <c r="J290" t="inlineStr"/>
-      <c r="K290" t="inlineStr"/>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -12346,10 +14074,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H291" t="inlineStr"/>
-      <c r="I291" t="inlineStr"/>
-      <c r="J291" t="inlineStr"/>
-      <c r="K291" t="inlineStr"/>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -12387,10 +14121,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr"/>
-      <c r="I292" t="inlineStr"/>
-      <c r="J292" t="inlineStr"/>
-      <c r="K292" t="inlineStr"/>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -12428,10 +14168,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr"/>
-      <c r="I293" t="inlineStr"/>
-      <c r="J293" t="inlineStr"/>
-      <c r="K293" t="inlineStr"/>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -12469,10 +14215,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H294" t="inlineStr"/>
-      <c r="I294" t="inlineStr"/>
-      <c r="J294" t="inlineStr"/>
-      <c r="K294" t="inlineStr"/>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -12510,10 +14262,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H295" t="inlineStr"/>
-      <c r="I295" t="inlineStr"/>
-      <c r="J295" t="inlineStr"/>
-      <c r="K295" t="inlineStr"/>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -12551,10 +14309,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H296" t="inlineStr"/>
-      <c r="I296" t="inlineStr"/>
-      <c r="J296" t="inlineStr"/>
-      <c r="K296" t="inlineStr"/>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -12592,10 +14356,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H297" t="inlineStr"/>
-      <c r="I297" t="inlineStr"/>
-      <c r="J297" t="inlineStr"/>
-      <c r="K297" t="inlineStr"/>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -12633,10 +14403,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H298" t="inlineStr"/>
-      <c r="I298" t="inlineStr"/>
-      <c r="J298" t="inlineStr"/>
-      <c r="K298" t="inlineStr"/>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -12674,10 +14450,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H299" t="inlineStr"/>
-      <c r="I299" t="inlineStr"/>
-      <c r="J299" t="inlineStr"/>
-      <c r="K299" t="inlineStr"/>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -12715,10 +14497,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H300" t="inlineStr"/>
-      <c r="I300" t="inlineStr"/>
-      <c r="J300" t="inlineStr"/>
-      <c r="K300" t="inlineStr"/>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -12756,10 +14544,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H301" t="inlineStr"/>
-      <c r="I301" t="inlineStr"/>
-      <c r="J301" t="inlineStr"/>
-      <c r="K301" t="inlineStr"/>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -12797,10 +14591,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H302" t="inlineStr"/>
-      <c r="I302" t="inlineStr"/>
-      <c r="J302" t="inlineStr"/>
-      <c r="K302" t="inlineStr"/>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -12838,10 +14638,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H303" t="inlineStr"/>
-      <c r="I303" t="inlineStr"/>
-      <c r="J303" t="inlineStr"/>
-      <c r="K303" t="inlineStr"/>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -12879,10 +14685,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H304" t="inlineStr"/>
-      <c r="I304" t="inlineStr"/>
-      <c r="J304" t="inlineStr"/>
-      <c r="K304" t="inlineStr"/>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -12920,10 +14732,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H305" t="inlineStr"/>
-      <c r="I305" t="inlineStr"/>
-      <c r="J305" t="inlineStr"/>
-      <c r="K305" t="inlineStr"/>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -12961,10 +14779,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H306" t="inlineStr"/>
-      <c r="I306" t="inlineStr"/>
-      <c r="J306" t="inlineStr"/>
-      <c r="K306" t="inlineStr"/>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -13002,10 +14826,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H307" t="inlineStr"/>
-      <c r="I307" t="inlineStr"/>
-      <c r="J307" t="inlineStr"/>
-      <c r="K307" t="inlineStr"/>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -13043,10 +14873,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H308" t="inlineStr"/>
-      <c r="I308" t="inlineStr"/>
-      <c r="J308" t="inlineStr"/>
-      <c r="K308" t="inlineStr"/>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -13084,10 +14920,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H309" t="inlineStr"/>
-      <c r="I309" t="inlineStr"/>
-      <c r="J309" t="inlineStr"/>
-      <c r="K309" t="inlineStr"/>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -13125,10 +14967,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H310" t="inlineStr"/>
-      <c r="I310" t="inlineStr"/>
-      <c r="J310" t="inlineStr"/>
-      <c r="K310" t="inlineStr"/>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -13166,10 +15014,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H311" t="inlineStr"/>
-      <c r="I311" t="inlineStr"/>
-      <c r="J311" t="inlineStr"/>
-      <c r="K311" t="inlineStr"/>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -13207,10 +15061,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H312" t="inlineStr"/>
-      <c r="I312" t="inlineStr"/>
-      <c r="J312" t="inlineStr"/>
-      <c r="K312" t="inlineStr"/>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -13248,10 +15108,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H313" t="inlineStr"/>
-      <c r="I313" t="inlineStr"/>
-      <c r="J313" t="inlineStr"/>
-      <c r="K313" t="inlineStr"/>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -13289,10 +15155,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H314" t="inlineStr"/>
-      <c r="I314" t="inlineStr"/>
-      <c r="J314" t="inlineStr"/>
-      <c r="K314" t="inlineStr"/>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -13330,10 +15202,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H315" t="inlineStr"/>
-      <c r="I315" t="inlineStr"/>
-      <c r="J315" t="inlineStr"/>
-      <c r="K315" t="inlineStr"/>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -13371,10 +15249,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr"/>
-      <c r="I316" t="inlineStr"/>
-      <c r="J316" t="inlineStr"/>
-      <c r="K316" t="inlineStr"/>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -13412,10 +15296,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H317" t="inlineStr"/>
-      <c r="I317" t="inlineStr"/>
-      <c r="J317" t="inlineStr"/>
-      <c r="K317" t="inlineStr"/>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -13453,10 +15343,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr"/>
-      <c r="I318" t="inlineStr"/>
-      <c r="J318" t="inlineStr"/>
-      <c r="K318" t="inlineStr"/>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -13494,10 +15390,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H319" t="inlineStr"/>
-      <c r="I319" t="inlineStr"/>
-      <c r="J319" t="inlineStr"/>
-      <c r="K319" t="inlineStr"/>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -13535,10 +15437,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H320" t="inlineStr"/>
-      <c r="I320" t="inlineStr"/>
-      <c r="J320" t="inlineStr"/>
-      <c r="K320" t="inlineStr"/>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -13576,10 +15484,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H321" t="inlineStr"/>
-      <c r="I321" t="inlineStr"/>
-      <c r="J321" t="inlineStr"/>
-      <c r="K321" t="inlineStr"/>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -13617,10 +15531,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H322" t="inlineStr"/>
-      <c r="I322" t="inlineStr"/>
-      <c r="J322" t="inlineStr"/>
-      <c r="K322" t="inlineStr"/>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -13658,10 +15578,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H323" t="inlineStr"/>
-      <c r="I323" t="inlineStr"/>
-      <c r="J323" t="inlineStr"/>
-      <c r="K323" t="inlineStr"/>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -13699,10 +15625,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr"/>
-      <c r="I324" t="inlineStr"/>
-      <c r="J324" t="inlineStr"/>
-      <c r="K324" t="inlineStr"/>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -13740,10 +15672,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H325" t="inlineStr"/>
-      <c r="I325" t="inlineStr"/>
-      <c r="J325" t="inlineStr"/>
-      <c r="K325" t="inlineStr"/>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -13781,10 +15719,16 @@
           <t>規則2 定居類語序（P02 上班）＋規則3 是非問句 NMS（P03），審核優先</t>
         </is>
       </c>
-      <c r="H326" t="inlineStr"/>
-      <c r="I326" t="inlineStr"/>
-      <c r="J326" t="inlineStr"/>
-      <c r="K326" t="inlineStr"/>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>語序需母語者確認（規則推導、語料無主流傾向可佐證）；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）；中文工作/上班對Gloss『上班』之語意(職業/活動/時段)需確認(codex audit)</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -13822,10 +15766,16 @@
           <t>自有實例 S14 我要喝水→我/水/喝/要 換主語＋規則3 是非問句 NMS，審核優先</t>
         </is>
       </c>
-      <c r="H327" t="inlineStr"/>
-      <c r="I327" t="inlineStr"/>
-      <c r="J327" t="inlineStr"/>
-      <c r="K327" t="inlineStr"/>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -13863,10 +15813,16 @@
           <t>自有實例 S15 我要上廁所→我/廁所/去/要 換主語＋規則3，審核優先</t>
         </is>
       </c>
-      <c r="H328" t="inlineStr"/>
-      <c r="I328" t="inlineStr"/>
-      <c r="J328" t="inlineStr"/>
-      <c r="K328" t="inlineStr"/>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -13904,10 +15860,16 @@
           <t>自有實例 S30 我要這個→我/這/要（這）＋S27 多少錢＋規則7 WH 句末，審核優先</t>
         </is>
       </c>
-      <c r="H329" t="inlineStr"/>
-      <c r="I329" t="inlineStr"/>
-      <c r="J329" t="inlineStr"/>
-      <c r="K329" t="inlineStr"/>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] WH句末符63%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -13945,10 +15907,16 @@
           <t>自有實例 S30 我要這個→我/這/要（這）＋S27 多少錢＋規則7 WH 句末，審核優先</t>
         </is>
       </c>
-      <c r="H330" t="inlineStr"/>
-      <c r="I330" t="inlineStr"/>
-      <c r="J330" t="inlineStr"/>
-      <c r="K330" t="inlineStr"/>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] WH句末符63%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
